--- a/files/Cases/RQ3_Summary_EventOmission_ForPhDThesis.xlsx
+++ b/files/Cases/RQ3_Summary_EventOmission_ForPhDThesis.xlsx
@@ -486,19 +486,19 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>28.57</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>185.5</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="H2" t="n">
-        <v>40.38</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +618,7 @@
         <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>31.33</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="7">
@@ -648,7 +648,7 @@
         <v>17.5</v>
       </c>
       <c r="H7" t="n">
-        <v>34.04</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="9">
@@ -702,13 +702,13 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G9" t="n">
         <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>44.1</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="10">
@@ -726,19 +726,19 @@
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>170.5</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="11">
@@ -855,7 +855,7 @@
         <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="H14" t="n">
         <v>12.24</v>
@@ -888,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="16">
@@ -918,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -942,13 +942,13 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>122.5</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="H17" t="n">
-        <v>5.14</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="18">
@@ -966,19 +966,19 @@
         <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="F18" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>24</v>
+        <v>20.5</v>
       </c>
       <c r="H18" t="n">
-        <v>20.49</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="19">
@@ -1005,10 +1005,10 @@
         <v>311</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>30.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>404</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>30.5</v>
       </c>
       <c r="H20" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="21">
@@ -1065,10 +1065,10 @@
         <v>404</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>30.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="22">
@@ -1176,19 +1176,19 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="F25" t="n">
-        <v>769</v>
+        <v>618</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>29.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.58</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="26">
@@ -1206,19 +1206,19 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>436</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>34.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="27">
@@ -1248,7 +1248,7 @@
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="28">
@@ -1278,7 +1278,7 @@
         <v>23</v>
       </c>
       <c r="H28" t="n">
-        <v>13.24</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="29">
@@ -1308,7 +1308,7 @@
         <v>29.5</v>
       </c>
       <c r="H29" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="30">
@@ -1338,7 +1338,7 @@
         <v>34</v>
       </c>
       <c r="H30" t="n">
-        <v>25.44</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="31">
@@ -1368,7 +1368,7 @@
         <v>37</v>
       </c>
       <c r="H31" t="n">
-        <v>18.08</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="32">
@@ -1398,7 +1398,7 @@
         <v>38</v>
       </c>
       <c r="H32" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="33">
@@ -1422,13 +1422,13 @@
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H33" t="n">
-        <v>15.08</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="34">
@@ -1575,10 +1575,10 @@
         <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="H38" t="n">
-        <v>27.78</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="39">
@@ -1605,7 +1605,7 @@
         <v>21</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H39" t="n">
         <v>31.25</v>
@@ -1686,19 +1686,19 @@
         <v>188</v>
       </c>
       <c r="D42" t="n">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>5.26</v>
       </c>
       <c r="F42" t="n">
-        <v>924</v>
+        <v>22070</v>
       </c>
       <c r="G42" t="n">
-        <v>65</v>
+        <v>6.5</v>
       </c>
       <c r="H42" t="n">
-        <v>6.72</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="43">
@@ -1725,10 +1725,10 @@
         <v>2668</v>
       </c>
       <c r="G43" t="n">
-        <v>53</v>
+        <v>374.75</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="44">
@@ -1755,10 +1755,10 @@
         <v>3269</v>
       </c>
       <c r="G44" t="n">
-        <v>75</v>
+        <v>478.5</v>
       </c>
       <c r="H44" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="45">
@@ -1785,10 +1785,10 @@
         <v>4867</v>
       </c>
       <c r="G45" t="n">
-        <v>80</v>
+        <v>682.25</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="46">
@@ -1815,10 +1815,10 @@
         <v>73</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="H46" t="n">
-        <v>18.45</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="47">
@@ -1836,19 +1836,19 @@
         <v>188</v>
       </c>
       <c r="D47" t="n">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="F47" t="n">
         <v>214</v>
       </c>
       <c r="G47" t="n">
-        <v>18</v>
+        <v>43.5</v>
       </c>
       <c r="H47" t="n">
-        <v>7.56</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="48">
@@ -1866,19 +1866,19 @@
         <v>188</v>
       </c>
       <c r="D48" t="n">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="F48" t="n">
         <v>510</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>32.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2.53</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1896,19 +1896,19 @@
         <v>188</v>
       </c>
       <c r="D49" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E49" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>96687.5</v>
+        <v>95712</v>
       </c>
       <c r="G49" t="n">
-        <v>271.5</v>
+        <v>1177.5</v>
       </c>
       <c r="H49" t="n">
-        <v>0.28</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="50">
@@ -1926,19 +1926,19 @@
         <v>29</v>
       </c>
       <c r="D50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
       </c>
       <c r="F50" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H50" t="n">
-        <v>18.59</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="51">
@@ -1968,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="H51" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="52">
@@ -1998,7 +1998,7 @@
         <v>15</v>
       </c>
       <c r="H52" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="53">
@@ -2028,7 +2028,7 @@
         <v>15</v>
       </c>
       <c r="H53" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="54">
@@ -2046,19 +2046,19 @@
         <v>29</v>
       </c>
       <c r="D54" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F54" t="n">
         <v>446</v>
       </c>
       <c r="G54" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H54" t="n">
-        <v>3.92</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="55">
@@ -2076,19 +2076,19 @@
         <v>29</v>
       </c>
       <c r="D55" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E55" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F55" t="n">
         <v>554</v>
       </c>
       <c r="G55" t="n">
-        <v>22</v>
+        <v>13.75</v>
       </c>
       <c r="H55" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="56">
@@ -2106,19 +2106,19 @@
         <v>29</v>
       </c>
       <c r="D56" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="F56" t="n">
         <v>703</v>
       </c>
       <c r="G56" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="57">
@@ -2142,13 +2142,13 @@
         <v>100</v>
       </c>
       <c r="F57" t="n">
-        <v>321.5</v>
+        <v>348</v>
       </c>
       <c r="G57" t="n">
         <v>15</v>
       </c>
       <c r="H57" t="n">
-        <v>4.67</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="58">
@@ -2166,19 +2166,19 @@
         <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F58" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G58" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="H58" t="n">
-        <v>47.92</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="59">
@@ -2355,10 +2355,10 @@
         <v>68</v>
       </c>
       <c r="G64" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H64" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="65">
@@ -2382,13 +2382,13 @@
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G65" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="H65" t="n">
-        <v>15.38</v>
+        <v>16.98</v>
       </c>
     </row>
   </sheetData>
@@ -2532,19 +2532,19 @@
         <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="F4" t="n">
         <v>740</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="5">
@@ -2622,19 +2622,19 @@
         <v>188</v>
       </c>
       <c r="D7" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>96.22</v>
       </c>
       <c r="F7" t="n">
         <v>97217</v>
       </c>
       <c r="G7" t="n">
-        <v>322</v>
+        <v>1326</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="8">
@@ -2958,19 +2958,19 @@
         <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>73.77</v>
       </c>
       <c r="F8" t="n">
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H8" t="n">
-        <v>44.44</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="9">
@@ -2988,19 +2988,19 @@
         <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="F9" t="n">
         <v>618</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>29.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.91</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="10">
@@ -3027,10 +3027,10 @@
         <v>869</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>30.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11">
@@ -3228,19 +3228,19 @@
         <v>188</v>
       </c>
       <c r="D17" t="n">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>53452</v>
       </c>
       <c r="G17" t="n">
-        <v>361</v>
+        <v>964.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.68</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="18">
@@ -3258,19 +3258,19 @@
         <v>188</v>
       </c>
       <c r="D18" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>95712</v>
       </c>
       <c r="G18" t="n">
-        <v>369</v>
+        <v>1177.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="19">
@@ -3288,19 +3288,19 @@
         <v>188</v>
       </c>
       <c r="D19" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>97.34</v>
       </c>
       <c r="F19" t="n">
         <v>173964</v>
       </c>
       <c r="G19" t="n">
-        <v>256</v>
+        <v>1519</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="20">
